--- a/dados_identificar.xlsx
+++ b/dados_identificar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1420A22-2486-4FF7-9B4D-AF6238C8470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941C02FE-5158-4189-BAE3-E48CD5A37A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="820">
   <si>
     <t>NaoIdentificado</t>
   </si>
@@ -1736,9 +1736,6 @@
     <t>RESUMO DO CONTRATO DE SUBVENÇÃO DE TARIFA No 092500703901 CONTRATANTE: Companhia Espírito Santense De Saneamento - CESAN. CONTRATADA: Associação Pestalozzi de Conceição da Barra OBJETO: O presente contrato tem por objeto o fornecimento de água para consumo e uso higiênico-sanitário e/ou coleta e tratamento de esgoto à ENTIDADE (matrícula 0375796-0), descrita na cláusula segunda e é regulado pelas condições estabelecidas neste instrumento, pelo Regulamento de Serviços Públicos de Água e Esgotos da CESAN e pela Norma Interna COM.006.07.2019, bem como pelas demais normas dirigidas aos clientes comuns. REF.: Processo no 2025-VWNDC Vitória, 12 de Janeiro de 2026. Fabio Ferreira da Costa Chefe da Divisão de Demandas Comerciais da CESAN</t>
   </si>
   <si>
-    <t>SubvenvaoTarifa</t>
-  </si>
-  <si>
     <t>RESUMO DO TERMO DE CONTRATO DE DOAÇÃO CONTRATO DE DOAÇÃO No. 029/2025 DOADOR: Secretaria de Estado de Saneamento, Habitação e Desenvolvimento Urbano - SEDURB. Processo no 2025-VK 4 XM. CNPJ/MF no. 08.673.715/0001-17. DONATÁRIO: MUNICÍPIO DE ALEGRE. CNPJ/MF no 27.174.101/0001-35. OBJETO: Caminhão Volkswagen, modelo VW 14.190 CRM 4 X 2, ano 2020/2021, motor diesel com 04 cilindros e potência 186 CV; PBT de 14.000 Kg, tração 4 x 2; direção hidráulica; caixa de marcha com 06 marchas à frente e 01 à ré; freios dianteiro e traseiro a tambor; pneus sem câmara com banda de rodagem mista terra e asfalto; cabine em aço na cor branca com assento pneumático; ar condicionado original do veículo e trava elétrica; tanque de combustível de 275 l; acessórios (estepe, macaco, chave de rodas, cones/triângulo); com equipamentos obrigatórios dentro das normas de segurança exigidos pelo Código de Trânsito Brasileiro - CTB e normas do Denatran com placa de identificação veicular: RBC 6 C 27, chassi: 9536 E 7236 MR 115498, número do motor 0155783 A 365780, Renavam: 1239270825 plaqueta de registro patrimonial: 68000000001369 e equipado com caixa coletora compactadora de resíduos sólidos urbanos, com capacidade de 10 m 3 de lixo compactado. Responsável pela assinatura: MARCOS AURÉLIO SOARES DA SILVA. Cargo: Secretário de Estado de Saneamento, Habitação e Desenvolvimento Urbano.</t>
   </si>
   <si>
@@ -2459,9 +2456,6 @@
     <t>ParalisacaoContrato</t>
   </si>
   <si>
-    <t>AutorizacaoServiços</t>
-  </si>
-  <si>
     <t>AtividadeRH</t>
   </si>
   <si>
@@ -2490,6 +2484,18 @@
   </si>
   <si>
     <t>conteudo_arquivo</t>
+  </si>
+  <si>
+    <t>SubvencaoTarifa</t>
+  </si>
+  <si>
+    <t>AvisoLicitacaoOutras</t>
+  </si>
+  <si>
+    <t>InstrucaoServicoDesignar</t>
+  </si>
+  <si>
+    <t>ResolucaoDesignar</t>
   </si>
 </sst>
 </file>
@@ -2862,21 +2868,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2894,7 +2900,7 @@
     </row>
     <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -2902,7 +2908,7 @@
     </row>
     <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -3020,7 +3026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -3038,7 +3044,7 @@
     </row>
     <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -3046,7 +3052,7 @@
     </row>
     <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -3062,7 +3068,7 @@
     </row>
     <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -3078,7 +3084,7 @@
     </row>
     <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B28" t="s">
         <v>39</v>
@@ -3116,7 +3122,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -3206,7 +3212,7 @@
     </row>
     <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B44" t="s">
         <v>59</v>
@@ -3230,7 +3236,7 @@
     </row>
     <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
@@ -3246,7 +3252,7 @@
     </row>
     <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B49" t="s">
         <v>64</v>
@@ -3302,7 +3308,7 @@
     </row>
     <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
@@ -3334,13 +3340,13 @@
     </row>
     <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B60" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3358,7 +3364,7 @@
     </row>
     <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B63" t="s">
         <v>83</v>
@@ -3430,7 +3436,7 @@
     </row>
     <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B72" t="s">
         <v>92</v>
@@ -3446,7 +3452,7 @@
     </row>
     <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B74" t="s">
         <v>94</v>
@@ -3470,7 +3476,7 @@
     </row>
     <row r="77" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B77" t="s">
         <v>97</v>
@@ -3518,7 +3524,7 @@
     </row>
     <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B83" t="s">
         <v>104</v>
@@ -3526,7 +3532,7 @@
     </row>
     <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B84" t="s">
         <v>105</v>
@@ -3534,7 +3540,7 @@
     </row>
     <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B85" t="s">
         <v>106</v>
@@ -3574,7 +3580,7 @@
     </row>
     <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B90" t="s">
         <v>112</v>
@@ -3614,7 +3620,7 @@
     </row>
     <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B95" t="s">
         <v>117</v>
@@ -3686,7 +3692,7 @@
     </row>
     <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B104" t="s">
         <v>127</v>
@@ -3702,7 +3708,7 @@
     </row>
     <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B106" t="s">
         <v>130</v>
@@ -3710,7 +3716,7 @@
     </row>
     <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B107" t="s">
         <v>131</v>
@@ -3750,7 +3756,7 @@
     </row>
     <row r="112" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B112" t="s">
         <v>136</v>
@@ -3774,7 +3780,7 @@
     </row>
     <row r="115" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B115" t="s">
         <v>139</v>
@@ -3782,7 +3788,7 @@
     </row>
     <row r="116" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B116" t="s">
         <v>140</v>
@@ -3822,7 +3828,7 @@
     </row>
     <row r="121" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B121" t="s">
         <v>146</v>
@@ -3900,7 +3906,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3942,7 +3948,7 @@
     </row>
     <row r="136" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B136" t="s">
         <v>163</v>
@@ -3950,7 +3956,7 @@
     </row>
     <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B137" t="s">
         <v>164</v>
@@ -3974,7 +3980,7 @@
     </row>
     <row r="140" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B140" t="s">
         <v>167</v>
@@ -4100,7 +4106,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="156" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -4110,7 +4116,7 @@
     </row>
     <row r="157" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B157" t="s">
         <v>186</v>
@@ -4140,7 +4146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="161" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -4166,7 +4172,7 @@
     </row>
     <row r="164" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B164" t="s">
         <v>193</v>
@@ -4190,7 +4196,7 @@
     </row>
     <row r="167" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B167" t="s">
         <v>196</v>
@@ -4198,7 +4204,7 @@
     </row>
     <row r="168" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B168" t="s">
         <v>197</v>
@@ -4212,7 +4218,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="170" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -4310,7 +4316,7 @@
     </row>
     <row r="182" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B182" t="s">
         <v>214</v>
@@ -4334,7 +4340,7 @@
     </row>
     <row r="185" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B185" t="s">
         <v>217</v>
@@ -4342,7 +4348,7 @@
     </row>
     <row r="186" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>5</v>
+        <v>817</v>
       </c>
       <c r="B186" t="s">
         <v>218</v>
@@ -4390,7 +4396,7 @@
     </row>
     <row r="192" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B192" t="s">
         <v>225</v>
@@ -4414,7 +4420,7 @@
     </row>
     <row r="195" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B195" t="s">
         <v>229</v>
@@ -4438,7 +4444,7 @@
     </row>
     <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B198" t="s">
         <v>232</v>
@@ -4534,7 +4540,7 @@
     </row>
     <row r="210" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B210" t="s">
         <v>244</v>
@@ -4550,7 +4556,7 @@
     </row>
     <row r="212" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B212" t="s">
         <v>246</v>
@@ -4606,7 +4612,7 @@
     </row>
     <row r="219" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B219" t="s">
         <v>253</v>
@@ -4614,13 +4620,13 @@
     </row>
     <row r="220" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B220" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="221" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -4710,7 +4716,7 @@
     </row>
     <row r="232" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B232" t="s">
         <v>267</v>
@@ -4726,7 +4732,7 @@
     </row>
     <row r="234" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B234" t="s">
         <v>269</v>
@@ -4766,7 +4772,7 @@
     </row>
     <row r="239" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B239" t="s">
         <v>275</v>
@@ -4814,7 +4820,7 @@
     </row>
     <row r="245" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B245" t="s">
         <v>281</v>
@@ -4822,7 +4828,7 @@
     </row>
     <row r="246" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B246" t="s">
         <v>282</v>
@@ -4870,7 +4876,7 @@
     </row>
     <row r="252" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B252" t="s">
         <v>288</v>
@@ -4934,7 +4940,7 @@
     </row>
     <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B260" t="s">
         <v>297</v>
@@ -4982,7 +4988,7 @@
     </row>
     <row r="266" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B266" t="s">
         <v>304</v>
@@ -5060,7 +5066,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="276" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>4</v>
       </c>
@@ -5142,7 +5148,7 @@
     </row>
     <row r="286" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B286" t="s">
         <v>325</v>
@@ -5150,7 +5156,7 @@
     </row>
     <row r="287" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B287" t="s">
         <v>326</v>
@@ -5166,7 +5172,7 @@
     </row>
     <row r="289" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B289" t="s">
         <v>328</v>
@@ -5190,7 +5196,7 @@
     </row>
     <row r="292" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B292" t="s">
         <v>331</v>
@@ -5206,7 +5212,7 @@
     </row>
     <row r="294" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B294" t="s">
         <v>333</v>
@@ -5214,7 +5220,7 @@
     </row>
     <row r="295" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B295" t="s">
         <v>334</v>
@@ -5268,7 +5274,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="302" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>4</v>
       </c>
@@ -5366,7 +5372,7 @@
     </row>
     <row r="314" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B314" t="s">
         <v>354</v>
@@ -5542,7 +5548,7 @@
     </row>
     <row r="336" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B336" t="s">
         <v>379</v>
@@ -5550,7 +5556,7 @@
     </row>
     <row r="337" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B337" t="s">
         <v>380</v>
@@ -5598,7 +5604,7 @@
     </row>
     <row r="343" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B343" t="s">
         <v>386</v>
@@ -5734,7 +5740,7 @@
     </row>
     <row r="360" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B360" t="s">
         <v>404</v>
@@ -5758,7 +5764,7 @@
     </row>
     <row r="363" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B363" t="s">
         <v>407</v>
@@ -5766,7 +5772,7 @@
     </row>
     <row r="364" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B364" t="s">
         <v>408</v>
@@ -5790,7 +5796,7 @@
     </row>
     <row r="367" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B367" t="s">
         <v>411</v>
@@ -5886,7 +5892,7 @@
     </row>
     <row r="379" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B379" t="s">
         <v>423</v>
@@ -5950,7 +5956,7 @@
     </row>
     <row r="387" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B387" t="s">
         <v>431</v>
@@ -5966,7 +5972,7 @@
     </row>
     <row r="389" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B389" t="s">
         <v>433</v>
@@ -5982,7 +5988,7 @@
     </row>
     <row r="391" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B391" t="s">
         <v>435</v>
@@ -5998,7 +6004,7 @@
     </row>
     <row r="393" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B393" t="s">
         <v>437</v>
@@ -6150,7 +6156,7 @@
     </row>
     <row r="412" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B412" t="s">
         <v>457</v>
@@ -6180,7 +6186,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="416" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>4</v>
       </c>
@@ -6220,7 +6226,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="421" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>4</v>
       </c>
@@ -6268,7 +6274,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="427" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>4</v>
       </c>
@@ -6356,7 +6362,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>364</v>
       </c>
@@ -6430,7 +6436,7 @@
     </row>
     <row r="447" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B447" t="s">
         <v>492</v>
@@ -6454,7 +6460,7 @@
     </row>
     <row r="450" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B450" t="s">
         <v>495</v>
@@ -6468,7 +6474,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="452" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>4</v>
       </c>
@@ -6492,7 +6498,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="455" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>4</v>
       </c>
@@ -6598,7 +6604,7 @@
     </row>
     <row r="468" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B468" t="s">
         <v>514</v>
@@ -6652,7 +6658,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="475" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>4</v>
       </c>
@@ -6739,7 +6745,7 @@
     </row>
     <row r="486" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B486" t="s">
         <v>533</v>
@@ -6763,7 +6769,7 @@
     </row>
     <row r="489" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B489" t="s">
         <v>536</v>
@@ -6835,7 +6841,7 @@
     </row>
     <row r="498" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B498" t="s">
         <v>545</v>
@@ -6843,7 +6849,7 @@
     </row>
     <row r="499" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B499" t="s">
         <v>546</v>
@@ -6899,7 +6905,7 @@
     </row>
     <row r="506" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B506" t="s">
         <v>553</v>
@@ -6947,7 +6953,7 @@
     </row>
     <row r="512" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B512" t="s">
         <v>559</v>
@@ -6979,7 +6985,7 @@
     </row>
     <row r="516" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B516" t="s">
         <v>563</v>
@@ -6995,7 +7001,7 @@
     </row>
     <row r="518" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>566</v>
+        <v>816</v>
       </c>
       <c r="B518" t="s">
         <v>565</v>
@@ -7006,7 +7012,7 @@
         <v>23</v>
       </c>
       <c r="B519" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="520" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7014,7 +7020,7 @@
         <v>9</v>
       </c>
       <c r="B520" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="521" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7022,7 +7028,7 @@
         <v>45</v>
       </c>
       <c r="B521" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="522" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7030,7 +7036,7 @@
         <v>35</v>
       </c>
       <c r="B522" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="523" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7038,15 +7044,15 @@
         <v>16</v>
       </c>
       <c r="B523" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="524" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B524" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="525" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7054,15 +7060,15 @@
         <v>16</v>
       </c>
       <c r="B525" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="526" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B526" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="527" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7070,7 +7076,7 @@
         <v>67</v>
       </c>
       <c r="B527" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="528" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7078,7 +7084,7 @@
         <v>79</v>
       </c>
       <c r="B528" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="529" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7086,31 +7092,31 @@
         <v>45</v>
       </c>
       <c r="B529" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="530" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B530" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="531" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B531" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="532" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B532" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="533" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7118,31 +7124,31 @@
         <v>29</v>
       </c>
       <c r="B533" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="534" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B534" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="535" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B535" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="536" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B536" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="537" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7150,7 +7156,7 @@
         <v>45</v>
       </c>
       <c r="B537" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="538" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7158,7 +7164,7 @@
         <v>300</v>
       </c>
       <c r="B538" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="539" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7166,7 +7172,7 @@
         <v>9</v>
       </c>
       <c r="B539" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="540" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7174,15 +7180,15 @@
         <v>25</v>
       </c>
       <c r="B540" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="541" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B541" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="542" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7190,7 +7196,7 @@
         <v>16</v>
       </c>
       <c r="B542" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="543" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7198,15 +7204,15 @@
         <v>16</v>
       </c>
       <c r="B543" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="544" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B544" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="545" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7214,7 +7220,7 @@
         <v>9</v>
       </c>
       <c r="B545" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="546" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7222,7 +7228,7 @@
         <v>67</v>
       </c>
       <c r="B546" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="547" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7230,15 +7236,15 @@
         <v>199</v>
       </c>
       <c r="B547" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="548" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B548" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="549" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7246,7 +7252,7 @@
         <v>79</v>
       </c>
       <c r="B549" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="550" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7254,15 +7260,15 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="551" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B551" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="552" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7270,7 +7276,7 @@
         <v>9</v>
       </c>
       <c r="B552" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="553" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7278,23 +7284,23 @@
         <v>16</v>
       </c>
       <c r="B553" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="554" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B554" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="555" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B555" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="556" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7302,15 +7308,15 @@
         <v>16</v>
       </c>
       <c r="B556" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="557" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>4</v>
       </c>
       <c r="B557" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="558" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7318,7 +7324,7 @@
         <v>100</v>
       </c>
       <c r="B558" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="559" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7326,15 +7332,15 @@
         <v>23</v>
       </c>
       <c r="B559" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="560" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B560" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="561" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7342,23 +7348,23 @@
         <v>5</v>
       </c>
       <c r="B561" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="562" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B562" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="563" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B563" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="564" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7366,7 +7372,7 @@
         <v>79</v>
       </c>
       <c r="B564" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="565" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7374,7 +7380,7 @@
         <v>25</v>
       </c>
       <c r="B565" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="566" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7382,23 +7388,23 @@
         <v>126</v>
       </c>
       <c r="B566" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="567" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B567" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="568" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B568" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="569" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7406,7 +7412,7 @@
         <v>16</v>
       </c>
       <c r="B569" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="570" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7414,7 +7420,7 @@
         <v>42</v>
       </c>
       <c r="B570" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="571" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7422,15 +7428,15 @@
         <v>16</v>
       </c>
       <c r="B571" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="572" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B572" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="573" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7438,7 +7444,7 @@
         <v>274</v>
       </c>
       <c r="B573" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="574" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7446,15 +7452,15 @@
         <v>5</v>
       </c>
       <c r="B574" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="575" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B575" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="576" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7462,7 +7468,7 @@
         <v>23</v>
       </c>
       <c r="B576" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="577" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7470,7 +7476,7 @@
         <v>5</v>
       </c>
       <c r="B577" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="578" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7478,7 +7484,7 @@
         <v>16</v>
       </c>
       <c r="B578" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="579" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7486,15 +7492,15 @@
         <v>13</v>
       </c>
       <c r="B579" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="580" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B580" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="581" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7502,7 +7508,7 @@
         <v>16</v>
       </c>
       <c r="B581" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="582" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7510,7 +7516,7 @@
         <v>13</v>
       </c>
       <c r="B582" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="583" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7518,7 +7524,7 @@
         <v>16</v>
       </c>
       <c r="B583" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="584" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7526,7 +7532,7 @@
         <v>25</v>
       </c>
       <c r="B584" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="585" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7534,7 +7540,7 @@
         <v>5</v>
       </c>
       <c r="B585" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="586" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7542,23 +7548,23 @@
         <v>2</v>
       </c>
       <c r="B586" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="587" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>4</v>
       </c>
       <c r="B587" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="588" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B588" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="589" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7566,7 +7572,7 @@
         <v>29</v>
       </c>
       <c r="B589" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="590" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7574,7 +7580,7 @@
         <v>16</v>
       </c>
       <c r="B590" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="591" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7582,7 +7588,7 @@
         <v>23</v>
       </c>
       <c r="B591" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="592" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7590,7 +7596,7 @@
         <v>70</v>
       </c>
       <c r="B592" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="593" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7598,7 +7604,7 @@
         <v>16</v>
       </c>
       <c r="B593" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="594" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7606,7 +7612,7 @@
         <v>16</v>
       </c>
       <c r="B594" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="595" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7614,7 +7620,7 @@
         <v>5</v>
       </c>
       <c r="B595" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="596" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7622,39 +7628,39 @@
         <v>13</v>
       </c>
       <c r="B596" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="597" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B597" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="598" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>35</v>
+        <v>806</v>
       </c>
       <c r="B598" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="599" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B599" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="600" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B600" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="601" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7662,7 +7668,7 @@
         <v>16</v>
       </c>
       <c r="B601" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="602" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7670,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="B602" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="603" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7678,15 +7684,15 @@
         <v>142</v>
       </c>
       <c r="B603" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>819</v>
+      </c>
+      <c r="B604" t="s">
         <v>654</v>
-      </c>
-    </row>
-    <row r="604" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A604" t="s">
-        <v>4</v>
-      </c>
-      <c r="B604" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="605" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7694,7 +7700,7 @@
         <v>16</v>
       </c>
       <c r="B605" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="606" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7702,7 +7708,7 @@
         <v>23</v>
       </c>
       <c r="B606" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="607" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7710,7 +7716,7 @@
         <v>79</v>
       </c>
       <c r="B607" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="608" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7718,31 +7724,31 @@
         <v>23</v>
       </c>
       <c r="B608" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="609" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B609" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="610" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B610" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="611" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B611" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="612" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7750,7 +7756,7 @@
         <v>35</v>
       </c>
       <c r="B612" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="613" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7758,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="B613" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="614" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7766,7 +7772,7 @@
         <v>5</v>
       </c>
       <c r="B614" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="615" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7774,15 +7780,15 @@
         <v>347</v>
       </c>
       <c r="B615" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="616" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B616" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="617" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7790,12 +7796,12 @@
         <v>23</v>
       </c>
       <c r="B617" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="618" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="B618" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="619" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7803,7 +7809,7 @@
         <v>79</v>
       </c>
       <c r="B619" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="620" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7811,7 +7817,7 @@
         <v>35</v>
       </c>
       <c r="B620" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="621" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7819,7 +7825,7 @@
         <v>45</v>
       </c>
       <c r="B621" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="622" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7827,15 +7833,15 @@
         <v>364</v>
       </c>
       <c r="B622" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>364</v>
       </c>
       <c r="B623" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="624" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7843,7 +7849,7 @@
         <v>364</v>
       </c>
       <c r="B624" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="625" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7851,7 +7857,7 @@
         <v>45</v>
       </c>
       <c r="B625" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="626" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7859,15 +7865,15 @@
         <v>45</v>
       </c>
       <c r="B626" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>364</v>
       </c>
       <c r="B627" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="628" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7875,15 +7881,15 @@
         <v>9</v>
       </c>
       <c r="B628" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>364</v>
       </c>
       <c r="B629" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="630" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7891,7 +7897,7 @@
         <v>45</v>
       </c>
       <c r="B630" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="631" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7899,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="B631" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="632" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7907,7 +7913,7 @@
         <v>25</v>
       </c>
       <c r="B632" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="633" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7915,7 +7921,7 @@
         <v>211</v>
       </c>
       <c r="B633" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="634" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7923,7 +7929,7 @@
         <v>13</v>
       </c>
       <c r="B634" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="635" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7931,7 +7937,7 @@
         <v>45</v>
       </c>
       <c r="B635" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="636" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7939,7 +7945,7 @@
         <v>42</v>
       </c>
       <c r="B636" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="637" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7947,15 +7953,15 @@
         <v>9</v>
       </c>
       <c r="B637" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="638" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B638" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="639" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7963,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="B639" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="640" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7971,7 +7977,7 @@
         <v>142</v>
       </c>
       <c r="B640" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="641" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7979,7 +7985,7 @@
         <v>265</v>
       </c>
       <c r="B641" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="642" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7987,7 +7993,7 @@
         <v>16</v>
       </c>
       <c r="B642" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="643" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -7995,7 +8001,7 @@
         <v>100</v>
       </c>
       <c r="B643" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="644" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8003,7 +8009,7 @@
         <v>25</v>
       </c>
       <c r="B644" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="645" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8011,7 +8017,7 @@
         <v>16</v>
       </c>
       <c r="B645" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="646" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8019,7 +8025,7 @@
         <v>16</v>
       </c>
       <c r="B646" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="647" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8027,7 +8033,7 @@
         <v>100</v>
       </c>
       <c r="B647" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="648" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8035,7 +8041,7 @@
         <v>16</v>
       </c>
       <c r="B648" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="649" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8043,7 +8049,7 @@
         <v>77</v>
       </c>
       <c r="B649" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="650" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8051,7 +8057,7 @@
         <v>79</v>
       </c>
       <c r="B650" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="651" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8059,15 +8065,15 @@
         <v>16</v>
       </c>
       <c r="B651" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>364</v>
       </c>
       <c r="B652" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="653" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8075,7 +8081,7 @@
         <v>5</v>
       </c>
       <c r="B653" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="654" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8083,7 +8089,7 @@
         <v>16</v>
       </c>
       <c r="B654" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="655" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8091,15 +8097,15 @@
         <v>16</v>
       </c>
       <c r="B655" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="656" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B656" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="657" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8107,39 +8113,39 @@
         <v>35</v>
       </c>
       <c r="B657" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="658" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B658" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="659" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B659" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="660" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B660" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="661" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B661" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="662" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8147,7 +8153,7 @@
         <v>79</v>
       </c>
       <c r="B662" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="663" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8155,7 +8161,7 @@
         <v>129</v>
       </c>
       <c r="B663" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="664" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8163,7 +8169,7 @@
         <v>23</v>
       </c>
       <c r="B664" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="665" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8171,7 +8177,7 @@
         <v>9</v>
       </c>
       <c r="B665" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="666" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8179,7 +8185,7 @@
         <v>9</v>
       </c>
       <c r="B666" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="667" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8187,15 +8193,15 @@
         <v>70</v>
       </c>
       <c r="B667" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="668" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B668" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="669" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8203,7 +8209,7 @@
         <v>67</v>
       </c>
       <c r="B669" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="670" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8211,7 +8217,7 @@
         <v>444</v>
       </c>
       <c r="B670" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="671" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8219,7 +8225,7 @@
         <v>5</v>
       </c>
       <c r="B671" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="672" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8227,7 +8233,7 @@
         <v>300</v>
       </c>
       <c r="B672" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="673" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8235,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="B673" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="674" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8243,7 +8249,7 @@
         <v>16</v>
       </c>
       <c r="B674" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="675" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8251,15 +8257,15 @@
         <v>16</v>
       </c>
       <c r="B675" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="676" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B676" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="677" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8267,7 +8273,7 @@
         <v>13</v>
       </c>
       <c r="B677" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="678" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8275,7 +8281,7 @@
         <v>42</v>
       </c>
       <c r="B678" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="679" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8283,7 +8289,7 @@
         <v>13</v>
       </c>
       <c r="B679" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="680" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8291,7 +8297,7 @@
         <v>16</v>
       </c>
       <c r="B680" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="681" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8299,7 +8305,7 @@
         <v>79</v>
       </c>
       <c r="B681" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="682" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8307,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="B682" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="683" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8315,15 +8321,15 @@
         <v>16</v>
       </c>
       <c r="B683" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="684" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B684" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="685" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8331,7 +8337,7 @@
         <v>16</v>
       </c>
       <c r="B685" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="686" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8339,7 +8345,7 @@
         <v>274</v>
       </c>
       <c r="B686" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="687" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8347,7 +8353,7 @@
         <v>23</v>
       </c>
       <c r="B687" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="688" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8355,7 +8361,7 @@
         <v>16</v>
       </c>
       <c r="B688" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="689" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8363,7 +8369,7 @@
         <v>23</v>
       </c>
       <c r="B689" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="690" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8371,7 +8377,7 @@
         <v>16</v>
       </c>
       <c r="B690" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="691" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8379,7 +8385,7 @@
         <v>16</v>
       </c>
       <c r="B691" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="692" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8387,7 +8393,7 @@
         <v>100</v>
       </c>
       <c r="B692" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="693" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8395,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="B693" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="694" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8403,15 +8409,15 @@
         <v>100</v>
       </c>
       <c r="B694" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="695" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B695" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="696" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8419,7 +8425,7 @@
         <v>13</v>
       </c>
       <c r="B696" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="697" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8427,7 +8433,7 @@
         <v>5</v>
       </c>
       <c r="B697" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="698" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8435,31 +8441,31 @@
         <v>42</v>
       </c>
       <c r="B698" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="699" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>807</v>
+        <v>35</v>
       </c>
       <c r="B699" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="700" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B700" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="701" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B701" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="702" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8467,7 +8473,7 @@
         <v>45</v>
       </c>
       <c r="B702" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="703" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8475,7 +8481,7 @@
         <v>45</v>
       </c>
       <c r="B703" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="704" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8483,7 +8489,7 @@
         <v>9</v>
       </c>
       <c r="B704" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="705" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8491,7 +8497,7 @@
         <v>29</v>
       </c>
       <c r="B705" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="706" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8499,7 +8505,7 @@
         <v>32</v>
       </c>
       <c r="B706" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="707" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8507,7 +8513,7 @@
         <v>79</v>
       </c>
       <c r="B707" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="708" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8515,7 +8521,7 @@
         <v>108</v>
       </c>
       <c r="B708" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="709" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8523,7 +8529,7 @@
         <v>16</v>
       </c>
       <c r="B709" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="710" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8539,7 +8545,7 @@
         <v>9</v>
       </c>
       <c r="B711" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="712" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8547,15 +8553,15 @@
         <v>16</v>
       </c>
       <c r="B712" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="713" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B713" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="714" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8563,23 +8569,23 @@
         <v>9</v>
       </c>
       <c r="B714" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="715" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B715" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="716" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B716" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="717" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8587,7 +8593,7 @@
         <v>45</v>
       </c>
       <c r="B717" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="718" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8595,15 +8601,15 @@
         <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="719" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B719" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="720" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8611,7 +8617,7 @@
         <v>100</v>
       </c>
       <c r="B720" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="721" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8619,7 +8625,7 @@
         <v>16</v>
       </c>
       <c r="B721" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="722" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8627,15 +8633,15 @@
         <v>16</v>
       </c>
       <c r="B722" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="723" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B723" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="724" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8643,7 +8649,7 @@
         <v>67</v>
       </c>
       <c r="B724" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="725" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8651,7 +8657,7 @@
         <v>79</v>
       </c>
       <c r="B725" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="726" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8659,7 +8665,7 @@
         <v>25</v>
       </c>
       <c r="B726" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="727" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8667,15 +8673,15 @@
         <v>25</v>
       </c>
       <c r="B727" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="728" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B728" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="729" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8683,7 +8689,7 @@
         <v>9</v>
       </c>
       <c r="B729" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="730" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8691,7 +8697,7 @@
         <v>25</v>
       </c>
       <c r="B730" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="731" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8699,7 +8705,7 @@
         <v>45</v>
       </c>
       <c r="B731" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="732" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8707,7 +8713,7 @@
         <v>67</v>
       </c>
       <c r="B732" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="733" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8715,7 +8721,7 @@
         <v>5</v>
       </c>
       <c r="B733" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="734" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8723,7 +8729,7 @@
         <v>79</v>
       </c>
       <c r="B734" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="735" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8731,7 +8737,7 @@
         <v>16</v>
       </c>
       <c r="B735" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="736" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8739,7 +8745,7 @@
         <v>29</v>
       </c>
       <c r="B736" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="737" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8747,15 +8753,15 @@
         <v>25</v>
       </c>
       <c r="B737" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="738" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B738" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="739" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8763,15 +8769,15 @@
         <v>45</v>
       </c>
       <c r="B739" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="740" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B740" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="741" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8779,7 +8785,7 @@
         <v>126</v>
       </c>
       <c r="B741" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="742" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8787,15 +8793,15 @@
         <v>5</v>
       </c>
       <c r="B742" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="743" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B743" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="744" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8803,7 +8809,7 @@
         <v>100</v>
       </c>
       <c r="B744" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="745" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8811,7 +8817,7 @@
         <v>13</v>
       </c>
       <c r="B745" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="746" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8819,7 +8825,7 @@
         <v>16</v>
       </c>
       <c r="B746" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="747" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8827,7 +8833,7 @@
         <v>42</v>
       </c>
       <c r="B747" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="748" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8835,15 +8841,15 @@
         <v>29</v>
       </c>
       <c r="B748" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="749" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="B749" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="750" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8851,7 +8857,7 @@
         <v>16</v>
       </c>
       <c r="B750" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="751" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
@@ -8859,14 +8865,14 @@
         <v>0</v>
       </c>
       <c r="B751" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C751" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="EditalFapes"/>
+        <filter val="Resolucao"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/dados_identificar.xlsx
+++ b/dados_identificar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941C02FE-5158-4189-BAE3-E48CD5A37A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96BA032-AC89-4983-9E46-4C4960EB8DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$751</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>77</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="141" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>77</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="274" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="B274" t="s">
         <v>313</v>
@@ -5066,7 +5066,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>4</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>4</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="383" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>77</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>4</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>4</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>4</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>4</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>4</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>4</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>4</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>4</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>819</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="649" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>77</v>
       </c>
@@ -8869,10 +8869,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C751" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:B751" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Resolucao"/>
+        <filter val="ErrataAvisoLicitacaoPregaoEletronico"/>
       </filters>
     </filterColumn>
   </autoFilter>
